--- a/results/Int All Data 0.2/Rando_4_permute.xlsx
+++ b/results/Int All Data 0.2/Rando_4_permute.xlsx
@@ -440,187 +440,187 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7555612920756768</v>
+        <v>0.743888794538229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7560622940796848</v>
+        <v>0.744389796542237</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7567253150368534</v>
+        <v>0.7693250908596854</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7535572840596447</v>
+        <v>0.7696491287660066</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7522013518562549</v>
+        <v>0.7698260928636935</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7525403349071024</v>
+        <v>0.7858007540504739</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7525403349071024</v>
+        <v>0.7762817159743216</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7525403349071024</v>
+        <v>0.7858007540504739</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7984752555959376</v>
+        <v>0.7846516762338236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8088342787269455</v>
+        <v>0.7794945823851092</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8088342787269455</v>
+        <v>0.7793325634319486</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8103372847389695</v>
+        <v>0.7798335654359566</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.81049930369213</v>
+        <v>0.7912370503719304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7899582215278014</v>
+        <v>0.7904120104616011</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7879542135117692</v>
+        <v>0.7949808090757786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7926551407900546</v>
+        <v>0.7959828130837947</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7968251757752793</v>
+        <v>0.815095614958731</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.790120240480962</v>
+        <v>0.8138718114194491</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7916381916375124</v>
+        <v>0.8106141095750823</v>
       </c>
     </row>
     <row r="21">
@@ -630,317 +630,317 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7999483713189091</v>
+        <v>0.8065911483984919</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7952773343296763</v>
+        <v>0.7989613124554193</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.800950375326925</v>
+        <v>0.7986223294045718</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8034404402024389</v>
+        <v>0.7861546822458476</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8032784212492783</v>
+        <v>0.7826028327842125</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8042804252572943</v>
+        <v>0.8016707992255698</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8042804252572943</v>
+        <v>0.8016707992255698</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8029543833429571</v>
+        <v>0.8019948371318909</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8029543833429571</v>
+        <v>0.7955266465133657</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8022465269522094</v>
+        <v>0.7970147073808634</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8004045378893381</v>
+        <v>0.7946866614585102</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8032485309602255</v>
+        <v>0.8126480078801671</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8042953704018205</v>
+        <v>0.811778132536259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8037794232532862</v>
+        <v>0.8104072551883428</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8037794232532862</v>
+        <v>0.8104072551883428</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7925953602119493</v>
+        <v>0.8126055500832172</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7910774090553989</v>
+        <v>0.8141085560952412</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.7991083862640536</v>
+        <v>0.8141085560952412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7827522842294758</v>
+        <v>0.8132536258958596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7660870894331036</v>
+        <v>0.8139315919975545</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7609150504398627</v>
+        <v>0.8139315919975545</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7710971094731837</v>
+        <v>0.8146095580992494</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7665880914371115</v>
+        <v>0.8135776638021807</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7610920145375497</v>
+        <v>0.8135776638021807</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7774630617166536</v>
+        <v>0.8124435311300566</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7774630617166536</v>
+        <v>0.8179844434631975</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7862891885465847</v>
+        <v>0.8186624095648924</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7906212424849699</v>
+        <v>0.8216534764444143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.800449373322917</v>
+        <v>0.8221544784484223</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7974583064433953</v>
+        <v>0.8280343738324105</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7941133113684997</v>
+        <v>0.8275184266838762</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7875853401718691</v>
+        <v>0.81472911925546</v>
       </c>
     </row>
     <row r="53">
@@ -950,1037 +950,1037 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7790934411195272</v>
+        <v>0.8296671308719132</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7811123942800856</v>
+        <v>0.8313321558370979</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7900407594850718</v>
+        <v>0.8266611188478652</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7876230426955606</v>
+        <v>0.8236551068238172</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7881240446995686</v>
+        <v>0.8222991746204273</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.788964029754424</v>
+        <v>0.8224313032845352</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7847192690465677</v>
+        <v>0.8243755307224618</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7803573248191298</v>
+        <v>0.8296498080907577</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7673139499337658</v>
+        <v>0.8290591352195917</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7660752012499575</v>
+        <v>0.816062973404436</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7657212730545837</v>
+        <v>0.8187300023776367</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7732087904622805</v>
+        <v>0.8175510342719337</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7732087904622805</v>
+        <v>0.8044353113005672</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7630267314289596</v>
+        <v>0.7952528786386333</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7599735063347033</v>
+        <v>0.810609354301824</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7601355252878639</v>
+        <v>0.8045823851092014</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7681366122074658</v>
+        <v>0.8067185217893413</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.779647090791753</v>
+        <v>0.7731238748683809</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7785954960768996</v>
+        <v>0.783276043612649</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7819829489487449</v>
+        <v>0.7862820556366972</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7793284874834414</v>
+        <v>0.7254689039095139</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7791664685302809</v>
+        <v>0.7144319146768112</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7792089263272307</v>
+        <v>0.7231683706395843</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7838178051017288</v>
+        <v>0.7718654257667878</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7792639516320777</v>
+        <v>0.7678574097347237</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7637257565979416</v>
+        <v>0.7575133317482422</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7719360755409124</v>
+        <v>0.7575133317482422</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7719360755409124</v>
+        <v>0.7462671104921708</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7565795998777216</v>
+        <v>0.7316161135830983</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7555477055806528</v>
+        <v>0.7438470160660304</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7803383037260962</v>
+        <v>0.7528602968649163</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7714924764783805</v>
+        <v>0.7502105906728711</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7744111952718997</v>
+        <v>0.755796338439591</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7463479501375632</v>
+        <v>0.7534234570836589</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7517764342243809</v>
+        <v>0.7534234570836589</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7127186576542917</v>
+        <v>0.7436527291871879</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.6987408715736558</v>
+        <v>0.7436527291871879</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6715624469277538</v>
+        <v>0.7355494038925308</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6628810162698278</v>
+        <v>0.7352104208416834</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6708545905370062</v>
+        <v>0.7268554057267076</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.6650918786725994</v>
+        <v>0.7331615773920723</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.656071464963826</v>
+        <v>0.7303301518290819</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6617468835977038</v>
+        <v>0.7143507353690431</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6505604429197378</v>
+        <v>0.7310159301654156</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6505604429197378</v>
+        <v>0.7233837165857138</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6706226011344724</v>
+        <v>0.7151907204238986</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.670373288950783</v>
+        <v>0.718343806256581</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6681199687510615</v>
+        <v>0.7107092150402501</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6855252878638634</v>
+        <v>0.688939574063381</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6855252878638634</v>
+        <v>0.6745803471349479</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6621629700078122</v>
+        <v>0.6791066879521755</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6618090418124385</v>
+        <v>0.6677409055398933</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.6568540470772053</v>
+        <v>0.6705251180326754</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.6566920281240447</v>
+        <v>0.6717190312829048</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.6417169933086512</v>
+        <v>0.6675340511531538</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.6498525865289901</v>
+        <v>0.6621850480622262</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.6551890221120207</v>
+        <v>0.6509687170952074</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.6487806120716009</v>
+        <v>0.6277283380319962</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.6445358513637445</v>
+        <v>0.5934485920994531</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.6268638972860976</v>
+        <v>0.5739203831391597</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.6278808464386401</v>
+        <v>0.5617044258007541</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6228983390509832</v>
+        <v>0.5617044258007541</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6250942563092287</v>
+        <v>0.5510685778336334</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6828307462382393</v>
+        <v>0.5585836078937536</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6828307462382393</v>
+        <v>0.5467168234774634</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6777161101864746</v>
+        <v>0.5512856220916409</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6926415542950307</v>
+        <v>0.5448897795591182</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.689059814544343</v>
+        <v>0.5299045548724568</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6769885533779423</v>
+        <v>0.5299045548724568</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.6769885533779423</v>
+        <v>0.5302435379233043</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6782996501477532</v>
+        <v>0.5309215040249992</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6993040317923984</v>
+        <v>0.5360660303658163</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.6845453619102613</v>
+        <v>0.5243188071057369</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7013348731361027</v>
+        <v>0.5266319078835637</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6812452022689447</v>
+        <v>0.5381549539757481</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6812452022689447</v>
+        <v>0.5602116096599979</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6809958900852553</v>
+        <v>0.571173873170069</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6555548384905403</v>
+        <v>0.5706728711660609</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5995754220305017</v>
+        <v>0.5706579260215345</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5666420977548317</v>
+        <v>0.565353758364186</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5668190618525186</v>
+        <v>0.5355232498896098</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5800394008355695</v>
+        <v>0.5318691620529193</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5833867735470942</v>
+        <v>0.5377490574369077</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5503355864270915</v>
+        <v>0.5349923575965491</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5198576814646242</v>
+        <v>0.5395761013552529</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5118966747053429</v>
+        <v>0.5136639380455826</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5120586936585034</v>
+        <v>0.5133249549947352</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5031554634693115</v>
+        <v>0.5162586189327808</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5005631602187426</v>
+        <v>0.5174525321830101</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4946234842566489</v>
+        <v>0.5198553038279949</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4966998403586835</v>
+        <v>0.5198553038279949</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4998828164804185</v>
+        <v>0.5340202438775857</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.499543833429571</v>
+        <v>0.5340202438775857</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5003838184844265</v>
+        <v>0.5366149247647838</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4993818144764104</v>
+        <v>0.5239278557114229</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4988808124724025</v>
+        <v>0.5207149893006352</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.501046839441595</v>
+        <v>0.5231452735980435</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4997207975272579</v>
+        <v>0.5111959512244829</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5021385143167691</v>
+        <v>0.5111959512244829</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5024326619340376</v>
+        <v>0.5104904724703645</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4992347406677762</v>
+        <v>0.4536578241228219</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4985567745660813</v>
+        <v>0.4619554362963215</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.501046839441595</v>
+        <v>0.4495798376413845</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5000597805781054</v>
+        <v>0.4993410549913386</v>
       </c>
     </row>
   </sheetData>
